--- a/assignments/wall/remarks_wall.xlsx
+++ b/assignments/wall/remarks_wall.xlsx
@@ -7182,8 +7182,10 @@
       <c r="U91" t="s">
         <v>123</v>
       </c>
-      <c r="V91" t="s">
-        <v>99</v>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
       </c>
       <c r="Y91" t="s">
         <v>259</v>
